--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,34 +30,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,27 +76,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,10 +472,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
@@ -509,18 +525,14 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Назначение: Управление процессом мультизаявки по некредитному страхованию</t>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Назначение: Управление процессом мультизаявки по некредитному страхованию. Источник правды: BPMN ump-main-ma-ncins-pa.bpmn (PR NCINS).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -531,11 +543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,12 +564,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Согласование</t>
         </is>
@@ -584,11 +600,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,7 +615,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -620,254 +631,260 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Минимальная информация для определения необходимости проведения НТ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="134" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[ump-main-ma-ncins-pa] Управление процессом мультизаявки по некредитному страхованию. Оркестратор: Call Activity prepare → Kafka stage DOCS_COMPLETED → signing → SIGN_COMPLETED → payment → (delete при timeout) → PAYMENT_COMPLETED → finalisation → COMPLETED. Event sub-process timer P30M → delete → BANK_REJECT.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Схема BPMN ump-main-ma-ncins-pa.bpmn; Confluence процесса</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>[ump-main-ma-ncins-pa] Оркестратор мультизаявки ncins (BPMN).
+Цепочка:
+1) Start (businessKey DYNAMIC, productCode≈NON_CREDIT_INSURANCE)
+2) Call Activity ump-prepare-documents-ncins-pa
+3) Kafka stage DOCS_COMPLETED (kafka-product-stage-outbound-connector)
+4) Call Activity ump-signing-documents-ncins-pa
+5) XOR: если timeoutMessage="TIMEOUT" → Call Activity ump-delete-documents-ncins-pa → product-status BANK_REJECT; иначе stage SIGN_COMPLETED
+6) Call Activity ump-payment-ncins-pa
+7) XOR: TIMEOUT → delete + BANK_REJECT; иначе stage PAYMENT_COMPLETED
+8) Call Activity ump-finalisation-ncins-pa → stage COMPLETED → End result=SUCCESS
+Event SubProcess: Timer PT30M → Call Activity ump-delete-documents-ncins-pa → BANK_REJECT (forcefullyTerminate=true).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Файл: bpmn/.../ump-main-ma-ncins-pa.bpmn</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>E2E SLA main — обсудить на встрече с НТ (ответ бэкенда). Ориентир СА для sync-шагов дочерних: несколько секунд на вызов. Таймеры: signing 25 мин, payment 5 мин, main 30 мин (аварийный).</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>E2E SLA main — TBD на встрече с НТ. Sync-шаги дочерних: несколько секунд/вызов (ориентир СА). Таймеры BPMN: signing PT25M, payment PT5M, main emergency PT30M.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>TBD числом с инженером НТ</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>База 15000 заявок/мес (SFA, рабочие часы ЮЛ). Среднее ≈ 89 заявок/час; максимальное (оценка пика ×2) ≈ 180 заявок/час. Профиль веток: ~95% normal / ~5% timeout (из timeout ~95% — signing).</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Способ расчёта: 15000 / ~21 р.д. / 8 ч ≈ 89/час; пик экспертно ×2. Timeout 5% — оценка сверху СА.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>База 15000 заявок/мес (SFA, рабочие часы ЮЛ). Среднее ≈89/час; пик (×2) ≈180/час. Профиль: ~95% happy-path / ~5% timeout (из timeout ~95% — signing).</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>15000/~21 р.д./8 ч ≈ 89/час; пик ×2</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>TBD (прогноз через 6 мес командой не зафиксирован; НТ-профиль уточнить с заказчиком/НТ).</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>TBD (прогноз через 6 мес не зафиксирован командой).</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>TBD макс/среднее через 6 мес</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Сервис/Коннектор/Процесс | ЧПН (оценка, вызовов/час ср./пик):
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Сервис/Процесс | ЧПН ср./пик (вызовов/час):
 [ump-prepare-documents-ncins-pa] ~89 / ~180
 [ump-signing-documents-ncins-pa] ~89 / ~180
 [ump-payment-ncins-pa] ~85 / ~170
 [ump-finalisation-ncins-pa] ~85 / ~170
-[ump-delete-documents-ncins-pa] ~4–5 / ~9
-[kafka-product-stage-outbound-connector] Обновить стадию ~89–180
-Kafka ump.process.to/from.system: до 1800 сообщений/день (бэкенд)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Может совпадать с ЧПН оркестратора по happy-path; delete — только timeout-ветки.</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+[ump-delete-documents-ncins-pa] ~4–5 / ~9 (только timeout)
+[kafka-product-stage-outbound-connector] ~89–180 (стадии DOCS/SIGN/PAYMENT/COMPLETED)
+[kafka-product-status-event-outbound-connector] ~4–5 (BANK_REJECT)
+Kafka signing/payment flow: ориентир до ~1800 msg/день (бэкенд).</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Happy-path = ЧПН оркестратора; delete только timeout</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TBD (пропорционально п.4). Пока ориентир = текущая таблица п.5.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>TBD (пропорционально п.4). Пока ориентир = п.5.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -883,7 +900,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -899,289 +916,807 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2. Полная информация для проведения НТ (заполняется, только если получено заключение от инженера о необходимости проведения НТ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="140" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>У воркера отсутствует HTTP-эндпоинт. Вызов напрямую в Camunda/Zeebe.
-Вход на старте: businessKey (DYNAMIC), productCode=NON_CREDIT_INSURANCE (передаётся на старте, для продукта фактически константа).
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>HTTP-эндпоинта нет. Старт через Camunda/Zeebe.
+Вход: businessKey (DYNAMIC UUID), productCode=NON_CREDIT_INSURANCE (STATIC для ncins).
 Map.of("businessKey", "&lt;uuid&gt;", "productCode", "NON_CREDIT_INSURANCE");
-client.newCreateInstanceCommand().bpmnProcessId("ump-main-ma-ncins-pa").latestVersion().variables(variables).send().join();</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Параметризация: набор businessKey на объём ≥ ЧПН. productCode — const.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+client.newCreateInstanceCommand().bpmnProcessId("ump-main-ma-ncins-pa")...</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Параметризация: набор businessKey ≥ ЧПН; productCode — const</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Happy-path End: result = SUCCESS.
-Timer reject: statusCode=BANK_REJECT, statusMessage="Превышено время ожидания", forcefullyTerminate=true, cancelUserTask=false.
-Ориентир SUCCESS rate 99.99% — уточнить с НТ.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Happy-path End: result=SUCCESS.
+Reject ends: statusCode=BANK_REJECT, statusMessage="Превышено время ожидания", forcefullyTerminate=true, cancelUserTask=false.
+SUCCESS rate ориентир 99.99% — TBD с НТ.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SUCCESS / BANK_REJECT</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Main напрямую сущности UMP-БД не меняет. Стадии/статусы продукта обновляются через Kafka-коннекторы (DOCS_COMPLETED, SIGN_COMPLETED, PAYMENT_COMPLETED, COMPLETED / BANK_REJECT).</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Данные в рамках работы метода не изменяются в UMP DB напрямую — меняются стадии через коннекторы.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Main напрямую UMP-БД не меняет. Стадии/статусы через Kafka-коннекторы: DOCS_COMPLETED → SIGN_COMPLETED → PAYMENT_COMPLETED → COMPLETED / BANK_REJECT.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Стадии продукта через outbound connectors</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Моки живут в дочерних процессах: EQ (payment) — замокан; ЭА (finalisation) — мок на НТ; AC delete — сейчас мок в BPMN.
-На НТ обязательно подкладывать Kafka completion для signing и payment (сейчас вручную; автоматизацию — с НТ).</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Список моков по дочерним + скрипт/инструкция publish в Kafka</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Моки в дочерних: EQ (payment), ЭА (finalisation, 3× ea-send), AC delete (пока мок).
+На НТ обязательно подкладывать Kafka completion для signing (SigningDocs) и payment (paymentFinished) с correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE".</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Моки дочерних + Kafka publish completion</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>По дочерним sync: несколько секунд/вызов. Async signing на НТ: несколько секунд, не более ~3 (уточнить с НТ). Payment message: почти мгновенно (+запас ~30с). Kafka flow: запас по 1800 msg/день.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>service sync ~несколько сек; kafka publish/consume — по стенду</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Sync дочерних: несколько секунд/вызов. Async signing на НТ: несколько секунд, ≤~3 (TBD). Payment message: почти мгновенно (+запас ~30с). Kafka: запас по ~1800 msg/день.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>sync ~несколько сек; kafka по стенду</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1) Happy-path E2E (~95%): start→prepare→DOCS_COMPLETED→signing→SIGN_COMPLETED→payment→PAYMENT_COMPLETED→finalisation→COMPLETED→SUCCESS.
-2) Signing timeout (~4.75%): нет completion→delete→BANK_REJECT.
-3) Payment timeout (малая доля): P5M→reject.
-4) Main emergency P30M (~0): delete→BANK_REJECT.
-Корреляция timer vs message: таймер всего процесса 30 мин (бэкенд).</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>План вызовов дочерних методов/коннекторов последовательно + доля timeout-веток 5%.</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1) Happy-path E2E (~95%): prepare→DOCS_COMPLETED→signing→SIGN_COMPLETED→payment→PAYMENT_COMPLETED→finalisation→COMPLETED→SUCCESS.
+2) Signing timeout (~4.75%): timeoutMessage=TIMEOUT→Call Activity delete→BANK_REJECT.
+3) Payment timeout (малая): то же через XOR после payment.
+4) Main emergency PT30M (~0): delete→BANK_REJECT.
+Корреляция async: businessKey."."NON_CREDIT_INSURANCE.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Последовательные Call Activity + доля timeout 5%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НТ пререквизиты :: Worker ump-main-ma-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Шаги из ump-main-ma-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>BPMN id</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Type / called process</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Ключевые параметры</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>STATIC / DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>StartEvent</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>startEvent</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC: businessKey; STATIC≈ productCode=NON_CREDIT_INSURANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>call-activity-prepare</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Prepare docs</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>calledElement: ump-prepare-documents-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC in; out: result</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>connector-stage-docs</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Stage DOCS_COMPLETED</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-stage-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>stageCode=DOCS_COMPLETED</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>STATIC: stage; DYNAMIC: businessKey/productCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>call-activity-signing</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Signing</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>calledElement: ump-signing-documents-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC; out: result / timeoutMessage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Gateway_13ehqon</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>XOR after signing</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>exclusiveGateway</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>timeoutMessage="TIMEOUT" → delete</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC: timeoutMessage</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>call-activity-delete*</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Delete docs</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>calledElement: ump-delete-documents-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>на timeout-ветках (+ PT30M)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC: businessKey, productCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>connector-stage-sign</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Stage SIGN_COMPLETED</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-stage-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SIGN_COMPLETED</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>call-activity-payment</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>calledElement: ump-payment-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC; out: result / timeoutMessage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Gateway_1j90rp8</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>XOR after payment</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>exclusiveGateway</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>TIMEOUT → delete</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC: timeoutMessage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>connector-stage-pay</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Stage PAYMENT_COMPLETED</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-stage-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>PAYMENT_COMPLETED</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>call-activity-finalisation</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Finalisation</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>calledElement: ump-finalisation-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>connector-stage-done</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Stage COMPLETED</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-stage-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>EventSubProcess timer</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Emergency timeout</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>timerEventDefinition PT30M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>→ delete → BANK_REJECT</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>STATIC: PT30M</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>status-reject</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>BANK_REJECT</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-status-event-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>statusCode=BANK_REJECT; forcefullyTerminate=true</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>STATIC status fields</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Методы и примеры (код)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -477,7 +478,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -493,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -525,10 +526,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Назначение: Управление процессом мультизаявки по некредитному страхованию. Источник правды: BPMN ump-main-ma-ncins-pa.bpmn (PR NCINS).</t>
+          <t>Назначение: оркестратор мультизаявки ncins. В develop ump-ncins-pa BPMN ump-main-ma-ncins-pa.bpmn ОТСУТСТВУЕТ (есть только 5 дочерних процессов). Ниже — по дочерним BPMN/воркерам + СА.</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -564,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -631,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -674,211 +675,196 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="134" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>[ump-main-ma-ncins-pa] Оркестратор мультизаявки ncins (BPMN).
-Цепочка:
-1) Start (businessKey DYNAMIC, productCode≈NON_CREDIT_INSURANCE)
-2) Call Activity ump-prepare-documents-ncins-pa
-3) Kafka stage DOCS_COMPLETED (kafka-product-stage-outbound-connector)
-4) Call Activity ump-signing-documents-ncins-pa
-5) XOR: если timeoutMessage="TIMEOUT" → Call Activity ump-delete-documents-ncins-pa → product-status BANK_REJECT; иначе stage SIGN_COMPLETED
-6) Call Activity ump-payment-ncins-pa
-7) XOR: TIMEOUT → delete + BANK_REJECT; иначе stage PAYMENT_COMPLETED
-8) Call Activity ump-finalisation-ncins-pa → stage COMPLETED → End result=SUCCESS
-Event SubProcess: Timer PT30M → Call Activity ump-delete-documents-ncins-pa → BANK_REJECT (forcefullyTerminate=true).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Файл: bpmn/.../ump-main-ma-ncins-pa.bpmn</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>[ump-main-ma-ncins-pa] Оркестратор (BPMN файла нет в develop).
+По дочерним процессам в репе: prepare → signing → payment → finalisation; на timeout — delete.
+Дочерние job types реализованы в ump-ncins-pa (*Worker.java).</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Нужен BPMN main-ma из отдельной ветки/PR</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>E2E SLA main — TBD на встрече с НТ. Sync-шаги дочерних: несколько секунд/вызов (ориентир СА). Таймеры BPMN: signing PT25M, payment PT5M, main emergency PT30M.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>TBD числом с инженером НТ</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>E2E TBD с НТ. Sync дочерних: несколько секунд. В develop payment timer = PT15M (BPMN).</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>База 15000 заявок/мес (SFA, рабочие часы ЮЛ). Среднее ≈89/час; пик (×2) ≈180/час. Профиль: ~95% happy-path / ~5% timeout (из timeout ~95% — signing).</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>15000/~21 р.д./8 ч ≈ 89/час; пик ×2</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>База нагрузки СА: 15000 заявок/мес SFA → ≈89/час среднее, пик ≈180/час. Timeout-ветки ~5% (из них ~95% signing).</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>89 / 180 в час</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>TBD (прогноз через 6 мес не зафиксирован командой).</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>TBD макс/среднее через 6 мес</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Сервис/Процесс | ЧПН ср./пик (вызовов/час):
-[ump-prepare-documents-ncins-pa] ~89 / ~180
-[ump-signing-documents-ncins-pa] ~89 / ~180
-[ump-payment-ncins-pa] ~85 / ~170
-[ump-finalisation-ncins-pa] ~85 / ~170
-[ump-delete-documents-ncins-pa] ~4–5 / ~9 (только timeout)
-[kafka-product-stage-outbound-connector] ~89–180 (стадии DOCS/SIGN/PAYMENT/COMPLETED)
-[kafka-product-status-event-outbound-connector] ~4–5 (BANK_REJECT)
-Kafka signing/payment flow: ориентир до ~1800 msg/день (бэкенд).</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Happy-path = ЧПН оркестратора; delete только timeout</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>prepare/signing ~89–180; payment/finalisation ~85–170; delete ~4–5.
+HTTP из дочерних: GET /applications/{id}; PUT /products/{id}; POST /v1/ins-contracts; внешние connectors (EA, transfer-control).</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>См. листы дочерних процессов</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>TBD (пропорционально п.4). Пока ориентир = п.5.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -900,7 +886,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -916,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -959,235 +945,227 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>HTTP-эндпоинта нет. Старт через Camunda/Zeebe.
-Вход: businessKey (DYNAMIC UUID), productCode=NON_CREDIT_INSURANCE (STATIC для ncins).
-Map.of("businessKey", "&lt;uuid&gt;", "productCode", "NON_CREDIT_INSURANCE");
-client.newCreateInstanceCommand().bpmnProcessId("ump-main-ma-ncins-pa")...</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Параметризация: набор businessKey ≥ ЧПН; productCode — const</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>HTTP нет. Zeebe create instance bpmnProcessId=ump-main-ma-ncins-pa.
+Vars: businessKey (UUID), productCode=NON_CREDIT_INSURANCE.
+ВНИМАНИЕ: BPMN main в develop-архиве нет — пример старта уточнить по ветке с main-ma.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>{"businessKey":"&lt;uuid&gt;","productCode":"NON_CREDIT_INSURANCE"}</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Happy-path End: result=SUCCESS.
-Reject ends: statusCode=BANK_REJECT, statusMessage="Превышено время ожидания", forcefullyTerminate=true, cancelUserTask=false.
-SUCCESS rate ориентир 99.99% — TBD с НТ.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Happy-path: result=SUCCESS. Reject: BANK_REJECT (по СА/предыдущему PR). В develop коде main нет.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>SUCCESS / BANK_REJECT</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Main напрямую UMP-БД не меняет. Стадии/статусы через Kafka-коннекторы: DOCS_COMPLETED → SIGN_COMPLETED → PAYMENT_COMPLETED → COMPLETED / BANK_REJECT.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Стадии продукта через outbound connectors</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Через дочерние: PUT products (policyLink), POST ins-contracts; стадии/Kafka — вне этого сервиса.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>policyLink / договор АБ</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Моки в дочерних: EQ (payment), ЭА (finalisation, 3× ea-send), AC delete (пока мок).
-На НТ обязательно подкладывать Kafka completion для signing (SigningDocs) и payment (paymentFinished) с correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE".</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Моки дочерних + Kafka publish completion</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Payment hold/create — stub в PaymentService. Delete AC — stub. EA/transfer — внешние connectors. Application facade / products / NIB — реальные Feign.</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>См. дочерние Excel</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Sync дочерних: несколько секунд/вызов. Async signing на НТ: несколько секунд, ≤~3 (TBD). Payment message: почти мгновенно (+запас ~30с). Kafka: запас по ~1800 msg/день.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>sync ~несколько сек; kafka по стенду</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Sync несколько секунд; async message на НТ сократить (≤~3 сек signing — по СА).</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>несколько сек</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1) Happy-path E2E (~95%): prepare→DOCS_COMPLETED→signing→SIGN_COMPLETED→payment→PAYMENT_COMPLETED→finalisation→COMPLETED→SUCCESS.
-2) Signing timeout (~4.75%): timeoutMessage=TIMEOUT→Call Activity delete→BANK_REJECT.
-3) Payment timeout (малая): то же через XOR после payment.
-4) Main emergency PT30M (~0): delete→BANK_REJECT.
-Корреляция async: businessKey."."NON_CREDIT_INSURANCE.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Последовательные Call Activity + доля timeout 5%</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>E2E по дочерним: prepare→signing→payment→finalisation; timeout→delete. Без BPMN main — тестировать дочерние по отдельности или подложить main из другой ветки.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>5 дочерних BPMN в develop</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -1204,15 +1182,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1225,14 +1203,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Шаги из ump-main-ma-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+          <t>Дочерние JobWorker в ump-ncins-pa (main BPMN отсутствует)</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1222,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN id</t>
+          <t>BPMN / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1254,465 +1232,241 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / called process</t>
+          <t>Type / HTTP</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ключевые параметры</t>
+          <t>Request / Input</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>STATIC / DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Response / Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>StartEvent</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>startEvent</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC: businessKey; STATIC≈ productCode=NON_CREDIT_INSURANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>businessKey, processType</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>getProcessParams + поля по типу</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-prepare</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Prepare docs</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-prepare-documents-ncins-pa</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC in; out: result</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>...get-report-data</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorker</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>локально XML→Base64</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>поля ПФ</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>documents[].reportData</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>connector-stage-docs</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Stage DOCS_COMPLETED</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-stage-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>stageCode=DOCS_COMPLETED</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>STATIC: stage; DYNAMIC: businessKey/productCode</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>update-product</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PUT /products/{id}</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>productId, acDocuments, productInfo</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>getProcessParams</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-signing</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Signing</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-signing-documents-ncins-pa</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC; out: result / timeoutMessage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>...set-hold / create-payment</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>STUB (нет HTTP)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Map variables</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>{"code":"SUCCESS"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Gateway_13ehqon</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>XOR after signing</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>exclusiveGateway</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>timeoutMessage="TIMEOUT" → delete</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC: timeoutMessage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>...create-contract</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>FinalisationWorker</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>ContractCreate vars</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>{"result":"SUCCESS"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-delete*</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Delete docs</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-delete-documents-ncins-pa</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>на timeout-ветках (+ PT30M)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC: businessKey, productCode</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>...delete-documents</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>DeleteDocumentsWorker</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>STUB AC 1.0</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>document.documentLink</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>{"documentResponse":{"status":"1"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>connector-stage-sign</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Stage SIGN_COMPLETED</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-stage-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>SIGN_COMPLETED</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-payment</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-payment-ncins-pa</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC; out: result / timeoutMessage</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Gateway_1j90rp8</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>XOR after payment</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>exclusiveGateway</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>TIMEOUT → delete</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC: timeoutMessage</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>connector-stage-pay</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Stage PAYMENT_COMPLETED</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-stage-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>PAYMENT_COMPLETED</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-finalisation</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Finalisation</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-finalisation-ncins-pa</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>connector-stage-done</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Stage COMPLETED</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-stage-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>EventSubProcess timer</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Emergency timeout</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>timerEventDefinition PT30M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>→ delete → BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>STATIC: PT30M</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>status-reject</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-status-event-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>statusCode=BANK_REJECT; forcefullyTerminate=true</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>STATIC status fields</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>внешние</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>ea-send / transfer-control</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>acId / messageName</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>вне ump-ncins-pa</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="220" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -958,19 +958,37 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>HTTP нет. Zeebe create instance bpmnProcessId=ump-main-ma-ncins-pa.
-Vars: businessKey (UUID), productCode=NON_CREDIT_INSURANCE.
-ВНИМАНИЕ: BPMN main в develop-архиве нет — пример старта уточнить по ветке с main-ma.</t>
+          <t>У воркера отсутствует HTTP-эндпоинт.
+Вызов происходит напрямую в Camunda.
+Camunda на базе Java скрипта, инструкция — https://confluence.moscow.alfaintra.net/pages/viewpage.action?pageId=2136656813
+Пример запроса:
+Map&lt;String, Object&gt; variables = Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003", // id заявки (UMP application)
+  "productCode", "NON_CREDIT_INSURANCE" // const
+);
+final ProcessInstanceEvent processInstanceEvent = client
+  .newCreateInstanceCommand()
+  .bpmnProcessId("ump-main-ma-ncins-pa")
+  .latestVersion()
+  .variables(variables)
+  .send()
+  .join();
+Параметры для запроса:
+1. businessKey — UUID заявки (параметризовать на объём ≥ ЧПН)
+2. productCode — const NON_CREDIT_INSURANCE (параметризация не нужна)
+ВНИМАНИЕ: BPMN main-ma в develop-архиве отсутствует — bpmnProcessId уточнить по ветке с оркестратором.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>{"businessKey":"&lt;uuid&gt;","productCode":"NON_CREDIT_INSURANCE"}</t>
+          <t>Map.of("businessKey","550e8400-...","productCode","NON_CREDIT_INSURANCE")</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
+          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.
+Параметризовать businessKey (≥ ЧПН). productCode — const NON_CREDIT_INSURANCE.
+Источник примеров: develop ump-ncins-pa *WorkerIT + stubs.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -979,7 +997,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="180" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -992,17 +1010,26 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Happy-path: result=SUCCESS. Reject: BANK_REJECT (по СА/предыдущему PR). В develop коде main нет.</t>
+          <t>Ответ как у HTTP-эндпоинта у воркера отсутствует (как в образце onboarding п.7).
+Ожидаемые исходы процесса (по дочерним + СА):
+- Happy-path End: result = SUCCESS
+- Timeout/reject: statusCode = BANK_REJECT, statusMessage = "Превышено время ожидания", forcefullyTerminate = true
+Дочерние HTTP (см. Excel prepare/finalisation):
+- GET /applications/{id} → 200 + ApplicationResponseDto
+- PUT /products/{id} → SUCCESS
+- POST /v1/ins-contracts → 201 {}</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SUCCESS / BANK_REJECT</t>
+          <t>SUCCESS / BANK_REJECT; дочерние 200/201</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
+          <t>Нужны примеры ответов, которые можно считать ожидаемыми.
+Например: getProcessParams=SUCCESS; HTTP 200/201; result=SUCCESS.
+Источник: *WorkerIT + stubs/ump/ump_application_response_200.json.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1171,6 +1198,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-main-ma-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -565,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -632,7 +639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -881,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -902,7 +909,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of) · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -1198,14 +1205,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1217,15 +1216,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1238,14 +1237,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>Полные request/response (не только имя метода). Источник: develop ump-ncins-pa@4a921a1653e + *WorkerIT + stubs. · полные HTTP body</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Дочерние JobWorker в ump-ncins-pa (main BPMN отсутствует)</t>
+          <t>HTTP / JobWorker — полные тела запросов и ответов</t>
         </is>
       </c>
     </row>
@@ -1257,251 +1256,687 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN / JobWorker</t>
+          <t>Метод / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Где</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / HTTP</t>
+          <t>Полный REQUEST (headers + body)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Request / Input</t>
+          <t>Полный RESPONSE (status + body)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Response / Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationDataWorker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>GET /applications/{id}</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>businessKey, processType</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>getProcessParams + поля по типу</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>get-application-data
+GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker
+все процессы</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET /applications/6dc5daf3-da12-4aae-9766-572da7b6b003?include=PARTICIPANT&amp;include=PRODUCT HTTP/1.1
+Host: ump-application-facade.ump.svc.cluster.local
+Accept: application/json
+(без body)
+Camunda job input:
+{
+  "businessKey": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "processType": "&lt;PREPARE_DOCUMENTS|SIGNING|PAYMENT|FINALISATION|DELETE_DOCS&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+{
+  "externalApplicationIds": [
+    {
+      "extAppId": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+      "systemCode": "SFA",
+      "extAppCreateDate": "2026-06-25T12:45:34.785179Z"
+    }
+  ],
+  "channels": [
+    {
+      "id": "bd458000-77c2-48af-91b4-815f7ef2d4e6",
+      "userInfo": {
+        "userId": "f6753df0-b5c9-4828-a7b7-f9f3f7d8f33c",
+        "login": "service-account-nib-corp-ncins"
+      },
+      "code": "nib-corp-ncins",
+      "name": "НИБ. Страхование",
+      "isDeleted": false,
+      "category": "RECEIVE",
+      "type": "BANK_SYSTEM"
+    }
+  ],
+  "participants": [
+    {
+      "id": "bdec62a5-e10a-4c5b-86c7-b5ac190b8055",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "isDeleted": false,
+      "contacts": [
+        {
+          "type": "EMAIL",
+          "typeName": "Email",
+          "value": "romashka@rambler.ru",
+          "isPrimary": false
+        },
+        {
+          "type": "PHONE",
+          "typeName": "Телефон",
+          "value": "79183221488",
+          "isPrimary": false
+        }
+      ],
+      "addresses": [
+        {
+          "type": "FACT",
+          "typeName": "Адрес проживания / фактический - краткий",
+          "address": {
+            "fullAddress": "Г. Пушкино ул. Колотушкина д. 14/88"
+          }
+        }
+      ],
+      "identityDocuments": [],
+      "okveds": [],
+      "licenses": [],
+      "management": [],
+      "founders": [],
+      "externalPins": [],
+      "pin": "AAAXYX",
+      "type": "LEGAL",
+      "typeName": "Юридическое лицо",
+      "fullName": "ООО Звезда",
+      "inn": "7826688577",
+      "createDate": "2026-07-09T17:19:18.963685Z",
+      "lastUpdateDate": "2026-07-09T17:19:19.99786Z",
+      "citizenship": "Россия",
+      "citizenshipCode": "RU",
+      "taxCountryCode": "RU",
+      "ogrn": "1027810281740"
+    }
+  ],
+  "products": [
+    {
+      "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "status": {
+        "isTerminate": true,
+        "code": "COMPLETE",
+        "name": "Завершен"
+      },
+      "stage": {
+        "code": "PAYMENT_COMPLETED",
+        "name": "PAYMENT_COMPLETED"
+      },
+      "createDate": "2026-07-09T17:19:18.891861Z",
+      "lastUpdateDate": "2026-07-09T17:23:50.600316Z",
+      "code": "NON_CREDIT_INSURANCE",
+      "name": "Некредитное страхование ЮЛ",
+      "type": "PRODUCT",
+      "main": false,
+      "isDeleted": false,
+      "responsibleManager": {
+        "login": "U_M13RU"
+      },
+      "salesChannel": {
+        "code": "SFA",
+        "name": "SFA"
+      },
+      "productProperties": {
+        "programId": 1073741824,
+        "beginDate": "2026-06-25T11:47:13.57Z",
+        "endDate": "2026-06-25T11:47:13.57Z",
+        "signDate": "2026-06-25T11:47:13.57Z",
+        "duration": 12,
+        "insuranceSum": 20000.0,
+        "insurancePremium": 20000.0,
+        "contractNumber": "1423423/sdf/123",
+        "paymentType": "payment_account",
+        "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+        "insuranceObjects": [
+          {
+            "paymentAccount": "123523464567347"
+          }
+        ],
+        "code": "NON_CREDIT_INSURANCE"
+      },
+      "channelCode": "nib-corp-ncins"
+    }
+  ],
+  "options": [],
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "createDate": "2026-07-09T17:19:18.833504Z",
+  "lastUpdateDate": "2026-07-09T17:22:46.462517Z",
+  "number": "UMP26070994592",
+  "statusCode": "COMPLETE",
+  "statusName": "Завершена",
+  "finalVersion": true,
+  "isDeleted": false
+}
+Camunda job output (успех):
+{ "getProcessParams": "SUCCESS", ...поля по processType из ApplicationMapper }
+Ошибка:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT
+stubs/ump/ump_application_response_200.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="372" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>...get-report-data</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>PrepareDataForPrintFormWorker</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>локально XML→Base64</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>поля ПФ</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>documents[].reportData</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ump-prepare-documents-ncins-pa.get-report-data
+(локально XML→Base64)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorker
+prepare</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-prepare-documents-ncins-pa.get-report-data
+HTTP: нет (локальная сборка XML + Base64)
+Camunda input (PrepareDataForPrintFormWorkerIT):
+{
+  "businessKey": "550e8400-e29b-41d4-a716-446655110003",
+  "programId": 1,
+  "fullName": "Иванов Иван Иванович",
+  "inn": "123456789012",
+  "email": "ivanov@example.com",
+  "contractNumber": "NC-2025-001",
+  "beginDate": "2025-01-01T00:00:00+03:00",
+  "endDate": "2026-01-01T00:00:00+03:00",
+  "currentDate": "2025-01-15",
+  "insuranceSum": 1000000.0,
+  "insurancePremium": 50000.0,
+  "paymentAccount": "40817810000000000001"
+}</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "serviceId": "550e8400-e29b-41d4-a716-446655110003",
+  "serviceCode": "APPLICATION",
+  "productCode": "NON_CREDIT_INSURANCE",
+  "documents": [
+    {
+      "documentType": "CONTRACT_ACCOUNT_BLOCK",
+      "reportData": "&lt;Base64 от XML ниже&gt;",
+      "isWriteInEa": false
+    }
+  ]
+}
+XML до Base64 (IT assert):
+&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;datasource&gt;
+  &lt;contractNumber&gt;NC-2025-001&lt;/contractNumber&gt;
+  &lt;fullName&gt;Иванов Иван Иванович&lt;/fullName&gt;
+  &lt;inn&gt;123456789012&lt;/inn&gt;
+  &lt;email&gt;ivanov@example.com&lt;/email&gt;
+  &lt;paymentAccount&gt;40817810000000000001&lt;/paymentAccount&gt;
+  &lt;insuranceSum&gt;1000000.00&lt;/insuranceSum&gt;
+  &lt;insurancePremium&gt;50000.00&lt;/insurancePremium&gt;
+  &lt;beginDate&gt;...&lt;/beginDate&gt;
+  &lt;endDate&gt;...&lt;/endDate&gt;
+  &lt;currentDate&gt;2025-01-15&lt;/currentDate&gt;
+&lt;/datasource&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorkerIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="332" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>update-product</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>ProductDataUpdateWorker</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>PUT /products/{id}</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>productId, acDocuments, productInfo</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>getProcessParams</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>update-product
+PUT /products/{id}</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker
+prepare</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>PUT /products/3d9fe175-2bc5-442a-b900-48522551de3f HTTP/1.1
+Host: ump-products.ump.svc.cluster.local
+Content-Type: application/json
+{
+  "code": "NON_CREDIT_INSURANCE",
+  "name": "Некредитное страхование ЮЛ",
+  "productProperties": {
+    "code": "NON_CREDIT_INSURANCE",
+    "programId": 1073741824,
+    "contractNumber": "1423423/sdf/123",
+    "beginDate": "2026-06-25T11:47:13.57Z",
+    "endDate": "2026-06-25T11:47:13.57Z",
+    "signDate": "2026-06-25T11:47:13.57Z",
+    "duration": 12,
+    "insuranceSum": 20000.0,
+    "insurancePremium": 20000.0,
+    "paymentType": "payment_account",
+    "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+    "policyLink": "770e8400-e29b-41d4-a716-446655110002",
+    "insuranceObjects": [
+      {
+        "paymentAccount": "123523464567347"
+      }
+    ]
+  }
+}
+Примечание: body = ProductCommonParamDto из productInfo;
+worker ДО вызова ставит productProperties.policyLink = acDocuments[0].acId.
+Живого JSON в IT нет (Mockito) — тело собрано по stub заявки + логике ProductDataUpdateWorker.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+ProductDto (возврат Feign; в IT не зафиксирован literal — обычно эхо обновлённого продукта).
+Camunda job output:
+{ "getProcessParams": "SUCCESS" }
+При exception:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker + stub заявки
+(IT без literal PUT body)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>...set-hold / create-payment</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>InsurancePaymentWorker</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>STUB (нет HTTP)</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Map variables</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>{"code":"SUCCESS"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.set-hold
+STUB (нет HTTP)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker
+payment</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-payment-ncins-pa.set-hold
+HTTP: нет (PaymentService TODO stub)
+Camunda input (InsurancePaymentWorkerIT):
+{
+  "businessKey": "550e8400-e29b-41d4-a716-446655110003",
+  "productCode": "NON_CREDIT_INSURANCE",
+  "systemCode": "SFA"
+}</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "code": "SUCCESS"
+}
+// message = null
+Ошибка:
+{ "code": "ERROR", "message": "&lt;text&gt;" }</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorkerIT
+PaymentService stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>...create-contract</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>FinalisationWorker</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>POST /v1/ins-contracts</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>ContractCreate vars</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>{"result":"SUCCESS"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.create-payment
+STUB (нет HTTP)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker
+payment</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-payment-ncins-pa.create-payment
+HTTP: нет (PaymentService TODO stub)
+Camunda input: тот же Map, что для set-hold (см. выше).</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "code": "SUCCESS"
+}
+// message = null
+Ошибка:
+{ "code": "ERROR", "message": "&lt;text&gt;" }</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorkerIT
+PaymentService stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="420" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>...delete-documents</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>DeleteDocumentsWorker</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>STUB AC 1.0</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>document.documentLink</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>{"documentResponse":{"status":"1"}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ump-finalisation-ncins-pa.create-contract
+POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>FinalisationWorker
+finalisation</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>POST /v1/ins-contracts HTTP/1.1
+Host: corp-gateway-test.moscow.alfaintra.net
+  /corp-ncins-acc-gateway/secure/corp-ncins-acc-corp-ncins-acc-api
+Content-Type: application/json
+A-userId: AAAX22
+A-customerId: AAAX22
+A-clientType: BACKEND
+A-channelId: ump
+A-projectId: ncins
+Authorization: Bearer &lt;keycloak access_token&gt;
+{
+  "programId": 3,
+  "contractNumber": "Z6922/888/ABR14880/10",
+  "beginDate": "2027-07-01T00:00:00Z",
+  "endDate": "2028-07-01T00:00:00Z",
+  "signDate": "2027-07-01T00:00:00Z",
+  "insuranceSum": 150000.93,
+  "insurancePremium": 50000.55,
+  "debitAccount": "40802810000000000000",
+  "duration": 12,
+  "paymentType": "payment_account",
+  "contractLink": "http://contract.link",
+  "policyLink": "http://policy.link",
+  "agreementLink": "http://agreement.link",
+  "sellerId": "ASASAS",
+  "sellerChannel": "SFA",
+  "owner": {
+    "inn": "7707083893",
+    "email": "romashka@rambler.ru",
+    "ownerId": "AAAX22",
+    "ogrn": null,
+    "phoneNumber": "+79001234567",
+    "legalAddress": "г. Пушкино ул. Колотушкина д. 14/88"
+  },
+  "insuranceObjects": [
+    {
+      "employeeFIO": "Иванов Иван Иванович",
+      "employeeEmail": "ivanov.ii@example.com",
+      "employeePhoneNumber": "+7 (999) 123-45-67",
+      "employeeBirthDate": "1985-05-15",
+      "paymentAccount": "40817810099910004312",
+      "cadastralNumber": "77:01:0001045:32",
+      "area": 45.5,
+      "realEstateAddress": "г. Москва, ул. Тверская, д. 15, кв. 78",
+      "realEstateType": "COMMERCIAL"
+    },
+    {
+      "employeeFIO": "Иванов Иван Иванович",
+      "employeeEmail": "ivanov.ii@example.com",
+      "employeePhoneNumber": "+7 (999) 123-45-67",
+      "employeeBirthDate": "1985-05-15",
+      "paymentAccount": "40817810099910004312",
+      "cadastralNumber": "77:01:0001045:32",
+      "area": 45.5,
+      "realEstateAddress": "г. Москва, ул. Тверская, д. 15, кв. 78",
+      "realEstateType": "RESIDENTIAL"
+    }
+  ]
+}
+Источник: FinalisationWorkerIT.createValidVariables + ContractMapper → ContractRequestDto.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 201 Created
+Content-Type: application/json
+{}
+Camunda job output:
+{
+  "result": "SUCCESS",
+  "errorMessage": null
+}
+HTTP 503 (после 3 retry):
+{
+  "result": "ERROR",
+  "errorMessage": "&lt;exception log&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>FinalisationWorkerIT
+ContractMapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="204" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>connectors</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>внешние</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>ea-send / transfer-control</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>acId / messageName</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>вне ump-ncins-pa</t>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ump-delete-documents-ncins-pa.delete-documents
+STUB AC 1.0</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>DeleteDocumentsWorker
+delete</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-delete-documents-ncins-pa.delete-documents
+HTTP: нет (DeleteDocumentsService TODO AC 1.0 stub)
+Camunda input (DeleteDocumentsWorkerIT / multiInstance element):
+{
+  "businessKey": "550e8400-e29b-41d4-a716-446655110000",
+  "document": {
+    "documentLink": "https://example.com/doc/123"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "documentResponse": {
+    "status": "1"
+  }
+}
+При exception:
+{
+  "documentResponse": {
+    "status": "2"
+  }
+}
+Реальный POST AlfaCapture deleteDocsh — TBD (stub).</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>DeleteDocumentsWorkerIT
+DeleteDocumentsService stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ump-document-connectors.ea-send-documents.v1
+×3 parallel</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>внешний connector
+finalisation</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Connector (вне ump-ncins-pa): ump-document-connectors.ea-send-documents.v1
+×3 параллельно после create-contract
+Input (BPMN):
+{
+  "acId": "&lt;agreementLink | policyLink | contractLink&gt;",
+  "stopInIncident": false
+}
+Полный HTTP body connector — в репе ncins нет (внешний модуль).</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Response необязателен.
+stopInIncident=false — отсутствие документов не обязано ронять в инцидент.
+Полный response TBD (модуль document-connectors).</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>BPMN finalisation
+(код connector вне репы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>ump-process-transfer-connector.transfer-control.v1</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>внешний connector
+signing</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Connector (вне ump-ncins-pa): ump-process-transfer-connector.transfer-control.v1
+BPMN inputs (develop):
+{
+  "stopInIncident": true,
+  "useProcessInstanceKey": true,
+  "systemCode": "&lt;productCode&gt;",
+  "messageName": "SigningDocs",
+  "applicationId": "&lt;businessKey&gt;"
+}
+Полный Kafka JSON to.system — TBD (внешний connector / аналитика).</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Далее receive message SigningDocs, correlationKey=processInstanceKey (develop).
+Payload from.system — TBD.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>BPMN signing
+(Kafka JSON TBD)</t>
         </is>
       </c>
     </row>
